--- a/packages/GB Accounts Self Employed 2021-04-05 (Apr21) Excel 2007/Fixedassets.xlsx
+++ b/packages/GB Accounts Self Employed 2021-04-05 (Apr21) Excel 2007/Fixedassets.xlsx
@@ -2166,7 +2166,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K8" s="7" t="str">
-        <f>IF(E8&gt;0,E8-J8," ")</f>
+        <f>IF(E8&gt;0,IF(V8&gt;0,0,E8-J8)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L8" s="7"/>
@@ -2216,7 +2216,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K9" s="7" t="str">
-        <f>IF(E9&gt;0,E9-J9," ")</f>
+        <f>IF(E9&gt;0,IF(V9&gt;0,0,E9-J9)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L9" s="7"/>
@@ -2266,7 +2266,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K10" s="7" t="str">
-        <f>IF(E10&gt;0,E10-J10," ")</f>
+        <f>IF(E10&gt;0,IF(V10&gt;0,0,E10-J10)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L10" s="7"/>
@@ -2455,7 +2455,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K14" s="7" t="str">
-        <f>IF(E14&gt;0,E14-J14," ")</f>
+        <f>IF(E14&gt;0,IF(V14&gt;0,0,E14-J14)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L14" s="7"/>
@@ -2517,7 +2517,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K15" s="7" t="str">
-        <f>IF(E15&gt;0,E15-J15," ")</f>
+        <f>IF(E15&gt;0,IF(V15&gt;0,0,E15-J15)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L15" s="7"/>
@@ -2579,7 +2579,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K16" s="7" t="str">
-        <f>IF(E16&gt;0,E16-J16," ")</f>
+        <f>IF(E16&gt;0,IF(V16&gt;0,0,E16-J16)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L16" s="7"/>
@@ -2641,7 +2641,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K17" s="7" t="str">
-        <f>IF(E17&gt;0,E17-J17," ")</f>
+        <f>IF(E17&gt;0,IF(V17&gt;0,0,E17-J17)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L17" s="7"/>
@@ -2703,7 +2703,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K18" s="7" t="str">
-        <f>IF(E18&gt;0,E18-J18," ")</f>
+        <f>IF(E18&gt;0,IF(V18&gt;0,0,E18-J18)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L18" s="7"/>
@@ -2904,7 +2904,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K22" s="7" t="str">
-        <f>IF(E22&gt;0,E22-J22," ")</f>
+        <f>IF(E22&gt;0,IF(V22&gt;0,0,E22-J22)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L22" s="7"/>
@@ -2966,7 +2966,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K23" s="7" t="str">
-        <f>IF(E23&gt;0,E23-J23," ")</f>
+        <f>IF(E23&gt;0,IF(V23&gt;0,0,E23-J23)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L23" s="7"/>
@@ -3028,7 +3028,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K24" s="7" t="str">
-        <f>IF(E24&gt;0,E24-J24," ")</f>
+        <f>IF(E24&gt;0,IF(V24&gt;0,0,E24-J24)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L24" s="7"/>
@@ -3090,7 +3090,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K25" s="7" t="str">
-        <f>IF(E25&gt;0,E25-J25," ")</f>
+        <f>IF(E25&gt;0,IF(V25&gt;0,0,E25-J25)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L25" s="7"/>
@@ -3152,7 +3152,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K26" s="7" t="str">
-        <f>IF(E26&gt;0,E26-J26," ")</f>
+        <f>IF(E26&gt;0,IF(V26&gt;0,0,E26-J26)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L26" s="7"/>
@@ -3353,7 +3353,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K30" s="7" t="str">
-        <f>IF(E30&gt;0,E30-J30," ")</f>
+        <f>IF(E30&gt;0,IF(V30&gt;0,0,E30-J30)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L30" s="7"/>
@@ -3415,7 +3415,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K31" s="7" t="str">
-        <f>IF(E31&gt;0,E31-J31," ")</f>
+        <f>IF(E31&gt;0,IF(V31&gt;0,0,E31-J31)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L31" s="7"/>
@@ -3477,7 +3477,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K32" s="7" t="str">
-        <f>IF(E32&gt;0,E32-J32," ")</f>
+        <f>IF(E32&gt;0,IF(V32&gt;0,0,E32-J32)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L32" s="7"/>
@@ -3539,7 +3539,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K33" s="7" t="str">
-        <f>IF(E33&gt;0,E33-J33," ")</f>
+        <f>IF(E33&gt;0,IF(V33&gt;0,0,E33-J33)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L33" s="7"/>
@@ -3601,7 +3601,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K34" s="7" t="str">
-        <f>IF(E34&gt;0,E34-J34," ")</f>
+        <f>IF(E34&gt;0,IF(V34&gt;0,0,E34-J34)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L34" s="7"/>
@@ -3805,7 +3805,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K38" s="7" t="str">
-        <f>IF(E38&gt;0,E38-J38," ")</f>
+        <f>IF(E38&gt;0,IF(V38&gt;0,0,E38-J38)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L38" s="7"/>
@@ -3869,7 +3869,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K39" s="7" t="str">
-        <f>IF(E39&gt;0,E39-J39," ")</f>
+        <f>IF(E39&gt;0,IF(V39&gt;0,0,E39-J39)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L39" s="7"/>
@@ -3933,7 +3933,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K40" s="7" t="str">
-        <f>IF(E40&gt;0,E40-J40," ")</f>
+        <f>IF(E40&gt;0,IF(V40&gt;0,0,E40-J40)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L40" s="7"/>
@@ -3997,7 +3997,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K41" s="7" t="str">
-        <f>IF(E41&gt;0,E41-J41," ")</f>
+        <f>IF(E41&gt;0,IF(V41&gt;0,0,E41-J41)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L41" s="7"/>
@@ -4061,7 +4061,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K42" s="7" t="str">
-        <f>IF(E42&gt;0,E42-J42," ")</f>
+        <f>IF(E42&gt;0,IF(V42&gt;0,0,E42-J42)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L42" s="7"/>
@@ -4159,7 +4159,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K44" s="7" t="str">
-        <f t="shared" ref="K44:K54" si="4">IF(E44&gt;0,E44-J44," ")</f>
+        <f t="shared" ref="K44:K54" si="4">IF(E44&gt;0,IF(V44&gt;0,0,E44-J44)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L44" s="7"/>
@@ -4287,7 +4287,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K46" s="7" t="str">
-        <f>IF(E46&gt;0,E46-J46," ")</f>
+        <f>IF(E46&gt;0,IF(V46&gt;0,0,E46-J46)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L46" s="7"/>
@@ -4351,7 +4351,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K47" s="7" t="str">
-        <f>IF(E47&gt;0,E47-J47," ")</f>
+        <f>IF(E47&gt;0,IF(V47&gt;0,0,E47-J47)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L47" s="7"/>
@@ -4415,7 +4415,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K48" s="7" t="str">
-        <f>IF(E48&gt;0,E48-J48," ")</f>
+        <f>IF(E48&gt;0,IF(V48&gt;0,0,E48-J48)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L48" s="7"/>
@@ -5109,7 +5109,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K61" s="7" t="str">
-        <f>IF(E61&gt;0,E61-J61," ")</f>
+        <f>IF(E61&gt;0,IF(V61&gt;0,0,E61-J61)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L61" s="7"/>
@@ -5156,7 +5156,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K62" s="7" t="str">
-        <f>IF(E62&gt;0,E62-J62," ")</f>
+        <f>IF(E62&gt;0,IF(V62&gt;0,0,E62-J62)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L62" s="7"/>
@@ -5203,7 +5203,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K63" s="7" t="str">
-        <f>IF(E63&gt;0,E63-J63," ")</f>
+        <f>IF(E63&gt;0,IF(V63&gt;0,0,E63-J63)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L63" s="7"/>
@@ -5389,7 +5389,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K67" s="7" t="str">
-        <f>IF(E67&gt;0,E67-J67," ")</f>
+        <f>IF(E67&gt;0,IF(V67&gt;0,0,E67-J67)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L67" s="7"/>
@@ -5451,7 +5451,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K68" s="7" t="str">
-        <f>IF(E68&gt;0,E68-J68," ")</f>
+        <f>IF(E68&gt;0,IF(V68&gt;0,0,E68-J68)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L68" s="7"/>
@@ -5513,7 +5513,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K69" s="7" t="str">
-        <f>IF(E69&gt;0,E69-J69," ")</f>
+        <f>IF(E69&gt;0,IF(V69&gt;0,0,E69-J69)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L69" s="7"/>
@@ -5575,7 +5575,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K70" s="7" t="str">
-        <f>IF(E70&gt;0,E70-J70," ")</f>
+        <f>IF(E70&gt;0,IF(V70&gt;0,0,E70-J70)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L70" s="7"/>
@@ -5637,7 +5637,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K71" s="7" t="str">
-        <f>IF(E71&gt;0,E71-J71," ")</f>
+        <f>IF(E71&gt;0,IF(V71&gt;0,0,E71-J71)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L71" s="7"/>
@@ -5838,7 +5838,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K75" s="7" t="str">
-        <f>IF(E75&gt;0,E75-J75," ")</f>
+        <f>IF(E75&gt;0,IF(V75&gt;0,0,E75-J75)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L75" s="7"/>
@@ -5900,7 +5900,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K76" s="7" t="str">
-        <f>IF(E76&gt;0,E76-J76," ")</f>
+        <f>IF(E76&gt;0,IF(V76&gt;0,0,E76-J76)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L76" s="7"/>
@@ -5962,7 +5962,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K77" s="7" t="str">
-        <f>IF(E77&gt;0,E77-J77," ")</f>
+        <f>IF(E77&gt;0,IF(V77&gt;0,0,E77-J77)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L77" s="7"/>
@@ -6024,7 +6024,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K78" s="7" t="str">
-        <f>IF(E78&gt;0,E78-J78," ")</f>
+        <f>IF(E78&gt;0,IF(V78&gt;0,0,E78-J78)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L78" s="7"/>
@@ -6086,7 +6086,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K79" s="7" t="str">
-        <f>IF(E79&gt;0,E79-J79," ")</f>
+        <f>IF(E79&gt;0,IF(V79&gt;0,0,E79-J79)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L79" s="7"/>
@@ -6287,7 +6287,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K83" s="7" t="str">
-        <f>IF(E83&gt;0,E83-J83," ")</f>
+        <f>IF(E83&gt;0,IF(V83&gt;0,0,E83-J83)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L83" s="7"/>
@@ -6349,7 +6349,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K84" s="7" t="str">
-        <f>IF(E84&gt;0,E84-J84," ")</f>
+        <f>IF(E84&gt;0,IF(V84&gt;0,0,E84-J84)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L84" s="7"/>
@@ -6411,7 +6411,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K85" s="7" t="str">
-        <f>IF(E85&gt;0,E85-J85," ")</f>
+        <f>IF(E85&gt;0,IF(V85&gt;0,0,E85-J85)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L85" s="7"/>
@@ -6473,7 +6473,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K86" s="7" t="str">
-        <f>IF(E86&gt;0,E86-J86," ")</f>
+        <f>IF(E86&gt;0,IF(V86&gt;0,0,E86-J86)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L86" s="7"/>
@@ -6535,7 +6535,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K87" s="7" t="str">
-        <f>IF(E87&gt;0,E87-J87," ")</f>
+        <f>IF(E87&gt;0,IF(V87&gt;0,0,E87-J87)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L87" s="7"/>
@@ -6740,7 +6740,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K91" s="7" t="str">
-        <f>IF(E91&gt;0,E91-J91," ")</f>
+        <f>IF(E91&gt;0,IF(V91&gt;0,0,E91-J91)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L91" s="7"/>
@@ -6801,7 +6801,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K92" s="7" t="str">
-        <f>IF(E92&gt;0,E92-J92," ")</f>
+        <f>IF(E92&gt;0,IF(V92&gt;0,0,E92-J92)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L92" s="7"/>
@@ -6862,7 +6862,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K93" s="7" t="str">
-        <f>IF(E93&gt;0,E93-J93," ")</f>
+        <f>IF(E93&gt;0,IF(V93&gt;0,0,E93-J93)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L93" s="7"/>
@@ -6923,7 +6923,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K94" s="7" t="str">
-        <f>IF(E94&gt;0,E94-J94," ")</f>
+        <f>IF(E94&gt;0,IF(V94&gt;0,0,E94-J94)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L94" s="7"/>
@@ -6984,7 +6984,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K95" s="7" t="str">
-        <f>IF(E95&gt;0,E95-J95," ")</f>
+        <f>IF(E95&gt;0,IF(V95&gt;0,0,E95-J95)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L95" s="7"/>
@@ -7080,7 +7080,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K97" s="7" t="str">
-        <f t="shared" ref="K97:K107" si="12">IF(E97&gt;0,E97-J97," ")</f>
+        <f t="shared" ref="K97:K107" si="12">IF(E97&gt;0,IF(V97&gt;0,0,E97-J97)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L97" s="7"/>
@@ -7202,7 +7202,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K99" s="7" t="str">
-        <f>IF(E99&gt;0,E99-J99," ")</f>
+        <f>IF(E99&gt;0,IF(V99&gt;0,0,E99-J99)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L99" s="7"/>
@@ -7263,7 +7263,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K100" s="7" t="str">
-        <f>IF(E100&gt;0,E100-J100," ")</f>
+        <f>IF(E100&gt;0,IF(V100&gt;0,0,E100-J100)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L100" s="7"/>
@@ -7324,7 +7324,7 @@
         <v xml:space="preserve"> </v>
       </c>
       <c r="K101" s="7" t="str">
-        <f>IF(E101&gt;0,E101-J101," ")</f>
+        <f>IF(E101&gt;0,IF(V101&gt;0,0,E101-J101)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="L101" s="7"/>
@@ -8782,7 +8782,7 @@
       <c r="G10" s="84"/>
       <c r="H10" s="90"/>
       <c r="I10" s="82" t="str">
-        <f>IF(H10&gt;0,#REF!/H10," ")</f>
+        <f>IF(E10&gt;0,(E10+F10+G10)/H10," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J10" s="82" t="str">
@@ -8821,7 +8821,7 @@
       <c r="G12" s="84"/>
       <c r="H12" s="90"/>
       <c r="I12" s="82" t="str">
-        <f>IF(H12&gt;0,#REF!/H12," ")</f>
+        <f>IF(E12&gt;0,(E12+F12+G12)/H12," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J12" s="82" t="str">
@@ -8860,7 +8860,7 @@
       <c r="G14" s="84"/>
       <c r="H14" s="90"/>
       <c r="I14" s="82" t="str">
-        <f>IF(H14&gt;0,#REF!/H14," ")</f>
+        <f>IF(E14&gt;0,(E14+F14+G14)/H14," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J14" s="82" t="str">
@@ -9056,7 +9056,7 @@
       <c r="G24" s="84"/>
       <c r="H24" s="90"/>
       <c r="I24" s="82" t="str">
-        <f>IF(H24&gt;0,#REF!/H24," ")</f>
+        <f>IF(E24&gt;0,(E24+F24+G24)/H24," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J24" s="82" t="str">
@@ -9095,7 +9095,7 @@
       <c r="G26" s="84"/>
       <c r="H26" s="90"/>
       <c r="I26" s="82" t="str">
-        <f>IF(H26&gt;0,#REF!/H26," ")</f>
+        <f>IF(E26&gt;0,(E26+F26+G26)/H26," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J26" s="82" t="str">
@@ -9134,7 +9134,7 @@
       <c r="G28" s="84"/>
       <c r="H28" s="90"/>
       <c r="I28" s="82" t="str">
-        <f>IF(H28&gt;0,#REF!/H28," ")</f>
+        <f>IF(E28&gt;0,(E28+F28+G28)/H28," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="J28" s="82" t="str">

--- a/packages/GB Accounts Self Employed 2021-04-05 (Apr21) Excel 2007/Fixedassets.xlsx
+++ b/packages/GB Accounts Self Employed 2021-04-05 (Apr21) Excel 2007/Fixedassets.xlsx
@@ -1357,14 +1357,7 @@
             <v>0.18</v>
           </cell>
         </row>
-        <row r="8">
-          <cell r="E8">
-            <v>12000</v>
-          </cell>
-          <cell r="G8">
-            <v>3000</v>
-          </cell>
-        </row>
+        <row r="8"/>
         <row r="13">
           <cell r="G13">
             <v>0</v>
@@ -3817,7 +3810,7 @@
       <c r="P38" s="88"/>
       <c r="Q38" s="11"/>
       <c r="R38" s="11" t="str">
-        <f>IF(O38&gt;0,MIN(O38*R$4*(1-M38),[1]Admin!$G$8*(1-M38))," ")</f>
+        <f>IF(O38&gt;0,O38*R$4*(1-M38)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S38" s="11" t="str">
@@ -3881,7 +3874,7 @@
       <c r="P39" s="88"/>
       <c r="Q39" s="11"/>
       <c r="R39" s="11" t="str">
-        <f>IF(O39&gt;0,MIN(O39*R$4*(1-M39),[1]Admin!$G$8*(1-M39))," ")</f>
+        <f>IF(O39&gt;0,O39*R$4*(1-M39)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S39" s="11" t="str">
@@ -3945,7 +3938,7 @@
       <c r="P40" s="88"/>
       <c r="Q40" s="11"/>
       <c r="R40" s="11" t="str">
-        <f>IF(O40&gt;0,MIN(O40*R$4*(1-M40),[1]Admin!$G$8*(1-M40))," ")</f>
+        <f>IF(O40&gt;0,O40*R$4*(1-M40)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S40" s="11" t="str">
@@ -4009,7 +4002,7 @@
       <c r="P41" s="88"/>
       <c r="Q41" s="11"/>
       <c r="R41" s="11" t="str">
-        <f>IF(O41&gt;0,MIN(O41*R$4*(1-M41),[1]Admin!$G$8*(1-M41))," ")</f>
+        <f>IF(O41&gt;0,O41*R$4*(1-M41)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S41" s="11" t="str">
@@ -4073,7 +4066,7 @@
       <c r="P42" s="88"/>
       <c r="Q42" s="11"/>
       <c r="R42" s="11" t="str">
-        <f>IF(O42&gt;0,MIN(O42*R$4*(1-M42),[1]Admin!$G$8*(1-M42))," ")</f>
+        <f>IF(O42&gt;0,O42*R$4*(1-M42)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S42" s="11" t="str">
@@ -4171,7 +4164,7 @@
       <c r="P44" s="88"/>
       <c r="Q44" s="11"/>
       <c r="R44" s="11" t="str">
-        <f>IF(O44&gt;0,MIN(O44*R$4*(1-M44),[1]Admin!$G$8*(1-M44))," ")</f>
+        <f>IF(O44&gt;0,O44*R$4*(1-M44)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S44" s="11" t="str">
@@ -4235,7 +4228,7 @@
       <c r="P45" s="88"/>
       <c r="Q45" s="11"/>
       <c r="R45" s="11" t="str">
-        <f>IF(O45&gt;0,MIN(O45*R$4*(1-M45),[1]Admin!$G$8*(1-M45))," ")</f>
+        <f>IF(O45&gt;0,O45*R$4*(1-M45)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S45" s="11" t="str">
@@ -4299,7 +4292,7 @@
       <c r="P46" s="88"/>
       <c r="Q46" s="11"/>
       <c r="R46" s="11" t="str">
-        <f>IF(O46&gt;0,MIN(O46*R$4*(1-M46),[1]Admin!$G$8*(1-M46))," ")</f>
+        <f>IF(O46&gt;0,O46*R$4*(1-M46)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S46" s="11" t="str">
@@ -4363,7 +4356,7 @@
       <c r="P47" s="88"/>
       <c r="Q47" s="11"/>
       <c r="R47" s="11" t="str">
-        <f>IF(O47&gt;0,MIN(O47*R$4*(1-M47),[1]Admin!$G$8*(1-M47))," ")</f>
+        <f>IF(O47&gt;0,O47*R$4*(1-M47)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S47" s="11" t="str">
@@ -4427,7 +4420,7 @@
       <c r="P48" s="88"/>
       <c r="Q48" s="11"/>
       <c r="R48" s="11" t="str">
-        <f>IF(O48&gt;0,MIN(O48*R$4*(1-M48),[1]Admin!$G$8*(1-M48))," ")</f>
+        <f>IF(O48&gt;0,O48*R$4*(1-M48)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S48" s="11" t="str">
@@ -6752,7 +6745,7 @@
       <c r="P91" s="88"/>
       <c r="Q91" s="11"/>
       <c r="R91" s="11" t="str">
-        <f>IF(E91&gt;0,MIN(E91*R$4*(1-M91),[1]Admin!$G$8*(1-M91))," ")</f>
+        <f>IF(E91&gt;0,E91*R$4*(1-M91)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S91" s="11" t="str">
@@ -6813,7 +6806,7 @@
       <c r="P92" s="88"/>
       <c r="Q92" s="11"/>
       <c r="R92" s="11" t="str">
-        <f>IF(E92&gt;0,MIN(E92*R$4*(1-M92),[1]Admin!$G$8*(1-M92))," ")</f>
+        <f>IF(E92&gt;0,E92*R$4*(1-M92)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S92" s="11" t="str">
@@ -6874,7 +6867,7 @@
       <c r="P93" s="88"/>
       <c r="Q93" s="11"/>
       <c r="R93" s="11" t="str">
-        <f>IF(E93&gt;0,MIN(E93*R$4*(1-M93),[1]Admin!$G$8*(1-M93))," ")</f>
+        <f>IF(E93&gt;0,E93*R$4*(1-M93)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S93" s="11" t="str">
@@ -6935,7 +6928,7 @@
       <c r="P94" s="88"/>
       <c r="Q94" s="11"/>
       <c r="R94" s="11" t="str">
-        <f>IF(E94&gt;0,MIN(E94*R$4*(1-M94),[1]Admin!$G$8*(1-M94))," ")</f>
+        <f>IF(E94&gt;0,E94*R$4*(1-M94)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S94" s="11" t="str">
@@ -6996,7 +6989,7 @@
       <c r="P95" s="88"/>
       <c r="Q95" s="11"/>
       <c r="R95" s="11" t="str">
-        <f>IF(E95&gt;0,MIN(E95*R$4*(1-M95),[1]Admin!$G$8*(1-M95))," ")</f>
+        <f>IF(E95&gt;0,E95*R$4*(1-M95)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S95" s="11" t="str">
@@ -7092,7 +7085,7 @@
       <c r="P97" s="88"/>
       <c r="Q97" s="11"/>
       <c r="R97" s="11" t="str">
-        <f>IF(E97&gt;0,MIN(E97*R$4*(1-M97),[1]Admin!$G$8*(1-M97))," ")</f>
+        <f>IF(E97&gt;0,E97*R$4*(1-M97)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S97" s="11" t="str">
@@ -7153,7 +7146,7 @@
       <c r="P98" s="88"/>
       <c r="Q98" s="11"/>
       <c r="R98" s="11" t="str">
-        <f>IF(E98&gt;0,MIN(E98*R$4*(1-M98),[1]Admin!$G$8*(1-M98))," ")</f>
+        <f>IF(E98&gt;0,E98*R$4*(1-M98)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S98" s="11" t="str">
@@ -7214,7 +7207,7 @@
       <c r="P99" s="88"/>
       <c r="Q99" s="11"/>
       <c r="R99" s="11" t="str">
-        <f>IF(E99&gt;0,MIN(E99*R$4*(1-M99),[1]Admin!$G$8*(1-M99))," ")</f>
+        <f>IF(E99&gt;0,E99*R$4*(1-M99)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S99" s="11" t="str">
@@ -7275,7 +7268,7 @@
       <c r="P100" s="88"/>
       <c r="Q100" s="11"/>
       <c r="R100" s="11" t="str">
-        <f>IF(E100&gt;0,MIN(E100*R$4*(1-M100),[1]Admin!$G$8*(1-M100))," ")</f>
+        <f>IF(E100&gt;0,E100*R$4*(1-M100)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S100" s="11" t="str">
@@ -7336,7 +7329,7 @@
       <c r="P101" s="88"/>
       <c r="Q101" s="11"/>
       <c r="R101" s="11" t="str">
-        <f>IF(E101&gt;0,MIN(E101*R$4*(1-M101),[1]Admin!$G$8*(1-M101))," ")</f>
+        <f>IF(E101&gt;0,E101*R$4*(1-M101)," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="S101" s="11" t="str">
